--- a/quick-dial-cards-editable.xlsx
+++ b/quick-dial-cards-editable.xlsx
@@ -1192,11 +1192,7 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Sync ▸ Setup can also push gain, RF power and locks with the frequency — check what it’s configured to send before syncing someone else’s pack.</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1353,79 +1349,85 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>RF Safety Mode: hold the [exit] key while switching the TX on -&gt; LCD flashes; it will not radiate while you set group/channel. Power-cycle to exit.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Hold [exit] + tap [▼] on the TX. UR2: 10 / 50 mW; UR1: 10 / 100 mW (G1/H4/J5; L3 = 10/50).</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Analog FM on a strict 25 kHz grid — a .0125 offset doesn’t exist here.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Upper J5 and all of L3 (614–698 MHz) are illegal post-repack — check the band label before accepting the unit.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  Analog FM on a strict 25 kHz grid — a .0125 offset doesn’t exist here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Upper J5 and all of L3 (614–698 MHz) are illegal post-repack — check the band label before accepting the unit.</t>
+          <t>•  Tonekey squelch (Radio ▸ Squelch ▸ Tonekey) should stay On.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  Tonekey squelch (Radio ▸ Squelch ▸ Tonekey) should stay On.</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>UHF-R user guide</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://content-files.shure.com/FileRepository/27a20023-4-1-uhf-r.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>UHF-R spec sheet</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://content-files.shure.com/Pubs/UHF/UHF-R_Spec_Sheet.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="13">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1436,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1509,11 +1511,7 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Here the transmitter is the rack (P10T) and the receiver is the bodypack (P10R+) — reverse of a mic.</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1670,71 +1668,62 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Use the P10T’s front-panel RF switch (per channel): RF off -&gt; power on -&gt; set the frequency -&gt; RF on (“Switch RF off and power on”, per guide).</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>10 / 50 / 100 mW selectable (some bands top out at 50 mW).</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  P10T and P10R+ must be the same band.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  P10T and P10R+ must be the same band.</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Switch RF off before powering up near other systems.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Switch RF off before powering up near other systems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>PSM1000 user guide</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>https://pubs.shure.com/view/guide/PSM1000/en-US.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B23:E23"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C29:E29"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1745,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1818,11 +1807,7 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Use Sony’s UWP-D Frequency List to map an assigned MHz -&gt; Group/Channel. Group 00 = coarse 125 kHz steps. Tip: hold [NFC SYNC] ≥ 4 s = Clear Channel Scan of the selected group.</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1884,102 +1869,98 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>[+]/[–] to GP/CH; hold [SET] until GROUP flashes -&gt; pick the TV-channel-number group (not 01–09); [SET]. 3CHANNEL flashes -&gt; [+]/[–] to the channel = assigned MHz; [SET]. Power-cycle to transmit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+          <t>[+]/[–] to GP/CH; hold [SET] until GROUP flashes -&gt; pick the TV-channel-number group (not 01–09); [SET].</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>CHANNEL flashes -&gt; [+]/[–] to the channel = assigned MHz; [SET]. Power-cycle to transmit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>PORTABLE RECEIVER  -  URX-P40 (portable diversity tuner)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Device</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Instruction</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Notes / Corrections</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Portable Receiver</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>URX-P40 (portable diversity tuner)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>[+]/[–] to GP/CH; hold [SET] to edit. Select the same TV-channel-number group, then the channel matching the MHz. 2Confirm the MHz on the OLED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="5" t="n">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>[+]/[–] to GP/CH; hold [SET] to edit. Select the same TV-channel-number group, then the channel matching the MHz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Confirm the MHz on the OLED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Or run NFC / IR SYNC (RX-&gt;TX) to copy the receiver’s freq to the transmitter.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>RF POWER &amp; SAFE POWER-ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>You’re already RF-off: GP/CH is set in transmission-stopped mode (hold SET+POWER). Only power-cycle to transmit once the freq is right.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Menu RF POWER: HIGH / LOW — UTX-B40/M40 30 / 5 mW; UTX-P40 (US) 40 / 5 mW; E/KR models 10 / 2 mW.</t>
         </is>
       </c>
     </row>
@@ -2008,6 +1989,18 @@
       <c r="A28" s="7" t="inlineStr">
         <is>
           <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>UWP frequency lists</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>https://pro.sony/support/res/manuals/4530/63d2501a47358304ae6fe7185a0a2c9c/45307382M.pdf</t>
         </is>
       </c>
     </row>
@@ -2015,15 +2008,18 @@
   <mergeCells count="10">
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="C29:E29"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2034,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2107,11 +2103,7 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Cross Remote / pairing carries the exact freq from RX to TX (pair: TX hold [POWER] + [–], or RF REMOTE ▸ PAIRING). Use the Sony DWX Frequency List for group mapping.</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -2268,71 +2260,92 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>You’re already RF-off: GP/CH is set in setting mode (hold SET while powering on = transmission stopped). Power-cycle to transmit after the freq is set.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>2 / 10 / 25 mW selectable (DWT-B03R).</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  TX band/block must match the RX or they won’t link.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  TX band/block must match the RX or they won’t link.</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  A small preset group shows only a few channels — move to the TV-channel group.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  A small preset group shows only a few channels — move to the TV-channel group.</t>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>DWR-S03D manual</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>https://pro.sony/ue_US/products/dwx-digital-series-receivers/dwr-s03d</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>DWT-B03R manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://pro.sony/ue_US/support-resources/dwt-b03r/manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>DWX frequency lists</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://pro.sony/support/res/manuals/5014/0e48ca6987dac8196bc7de9ebb981c26/50148920M.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B23:E23"/>
+  <mergeCells count="14">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2343,7 +2356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2416,11 +2429,7 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>If the freq won’t change, the active group/channel is locked — switch to an unlocked one (locks are managed in Wisycom Manager).</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -2577,76 +2586,735 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Power up with transmission disabled — MTP60: hold EXIT/OFF to switch on without RF (or set RF Power = OFF); MTP40S: leave the wireless switch off. LED2 RED = RF off; set the freq, then enable a power level — LED2 GREEN = radiating.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>MTP60: 10 / L10 / 20 / L20 / 50 / 100 mW (+ OFF). MTP40S: 10 / 20 / 50 / 100 mW. (RF ▸ Power)</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Enable RF — wireless power switch to I (LED green). Set the correct battery type.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  Enable RF — wireless power switch to I (LED green). Set the correct battery type.</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Keep one open group for field tuning; locks live in Wisycom Manager.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Keep one open group for field tuning; locks live in Wisycom Manager.</t>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>MTP60 manual</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>https://wisycom.com/app/uploads/2024/03/MTP60-en-u07.pdf</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>MTP40S manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://wisycom.com/app/uploads/2024/10/MTP40S-en-u09-A5.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>MCR42 manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://wisycom.com/app/uploads/2018/06/MCR42-en-u15-A5.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B23:E23"/>
+  <mergeCells count="14">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lectrosonics Digital Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Block UHF · portable (slot) receiver shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>How to reach any MHz</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FREE-TUNE WITHIN BLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tuning step</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>25 or 100 kHz — selectable on the unit (Channel Spacing setup)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Range / band</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fixed BLOCK on the housing (470, 19, 21, 22…)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Matching TX &lt;-&gt; RX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TRANSMITTER  -  SMV / SMQV (and SMa, SSM, HMa plug-on…)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>SMV / SMQV (and SMa, SSM, HMa plug-on…)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>From home, press and HOLD [FREQ]; while holding, [UP]/[DOWN] moves the freq in 100 kHz steps. Release to set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Press [FREQ] again to toggle the display between MHz and the 2-digit hex channel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>To set with RF off, boot Standby: with power OFF, briefly press [AUDIO]+[FREQ] together — boots showing “rf OFF”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PORTABLE RECEIVER  -  SRc / SRc5P (2-ch slot receiver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Portable Receiver</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>SRc / SRc5P (2-ch slot receiver)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Press [MENU/SEL] to open setup; pick the receiver (1 or 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Hold [MENU/SEL] + [UP]/[DOWN] to step the frequency (or use SCAN, then set).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Then trigger IR SYNC to copy the receiver’s freq to the transmitter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RF POWER &amp; SAFE POWER-ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  If TX and RX blocks differ, they will never link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Spacing defaults to 100 kHz — set Channel Spacing = 25 kHz (setup menu / LectroRM) to reach .025 / .050 / .075 assignments. Hex is just a display format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>•  Blocks run past TV-band UHF — Block 944 (legacy, 944.100–951.900) and current -941 variants (941.525–951.975) = the STL band; same tuning drill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SMV/SMQV manual (Standby)</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3331/SMV_Series_man_ALL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SRc manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3382/SRc5P_SRc_ALL_man.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lectrosonics L-Series wideband</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Digital Hybrid UHF · spans 3 legacy blocks · portable receiver shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>How to reach any MHz</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FREE-TUNE WITHIN BLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tuning step</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>100 kHz default — set Step Size = 25 kHz</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Range / band</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>A1 470.100–537.575 · B1 537.600–607.950 (US TX; RX tunes to 614.3) · C1 614.400–691.175 (each unit covers one 3-block range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Matching TX &lt;-&gt; RX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TRANSMITTER  -  LT / LMb / SMWB / SMDWB (wideband bodypacks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>LT / LMb / SMWB / SMDWB (wideband bodypacks)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Power on in Standby Mode: short-press the power button, releasing before the countdown reaches 3 — RF stays off (“Standby” in the Main Window) while you tune.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Menu -&gt; StepSize: set 25 kHz. Then Frequency: [UP]/[DOWN] to the assigned MHz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Rf On from the Main / Power menu once confirmed — or IR-sync from the LR first, then enable RF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PORTABLE RECEIVER  -  LR (camera-mount receiver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Portable Receiver</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>LR (camera-mount receiver)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>[MENU/SEL] -&gt; set Step Size = 25 kHz, then open Frequency (or run SmartTune to scan for clear air).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Dial the same assigned MHz; confirm on the LCD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Trigger IR sync at the transmitter (RX -&gt; TX) — it carries frequency, step size and compat mode in one go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RF POWER &amp; SAFE POWER-ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Reports list these as “Lectrosonics 3 Block A1 / B1” — the wideband LT / LR / SMWB family (SMWB/SMDWB tune the same way; “Nu Hybrid” on a report = these in Digital Hybrid compat), not the single-block SMV card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Step Size left at 100 kHz silently hides .025 / .050 / .075 assignments — set 25 kHz on both TX and RX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>•  Compat mode (Digital Hybrid / 100 / 200 / IFB / Mode 3…) must match the receiver or no audio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>LT manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3328/LTman_ALL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>LR manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3376/LRman.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2665,14 +3333,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lectrosonics Digital Hybrid</t>
+          <t>Lectrosonics IFB (IFBlue)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Block UHF · portable (slot) receiver shown</t>
+          <t>Block UHF/VHF IFB — talent &amp; crew cue feeds · portable receiver shown</t>
         </is>
       </c>
     </row>
@@ -2703,7 +3371,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>25 or 100 kHz — selectable on the unit (Channel Spacing setup)</t>
+          <t>25 / 100 kHz (VHF 175 kHz)</t>
         </is>
       </c>
     </row>
@@ -2715,7 +3383,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Fixed BLOCK on the housing (470, 19, 21, 22…)</t>
+          <t>Fixed ~75 MHz range; RX &amp; TX ranges must match (A1 470–537, B1 537–614, C1 614–692; VHF 174–216; “-941” 941.5–952)</t>
         </is>
       </c>
     </row>
@@ -2725,16 +3393,12 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Block = the fixed hardware range; it can’t be changed in the field on single-block units. Match TX and RX blocks. (The SRc is itself a 3-block wideband RX — set its STEPSIZE 25/100 to match.)</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TRANSMITTER  -  SMV / SMQV (and SMa, SSM, HMa plug-on…)</t>
+          <t>TRANSMITTER  -  IFBT4 / IFBT2.0 (or any Lectro DH TX in IFB mode)</t>
         </is>
       </c>
     </row>
@@ -2773,7 +3437,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>SMV / SMQV (and SMa, SSM, HMa plug-on…)</t>
+          <t>IFBT4 / IFBT2.0 (or any Lectro DH TX in IFB mode)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -2781,7 +3445,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>From home, press and HOLD [FREQ]; while holding, [UP]/[DOWN] moves the freq in 100 kHz steps. Release to set.</t>
+          <t>IFBT4: set the switch to TUNE (RF off — freq changes only in TUNE). Set COMPAT to match the RX (IFB is the default).</t>
         </is>
       </c>
     </row>
@@ -2791,7 +3455,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Press [FREQ] again to toggle the display between MHz and the 2-digit hex channel.</t>
+          <t>Press [MENU] to the Frequency window; [UP]/[DOWN] to the assigned MHz ([MENU]+[UP]/[DOWN] jumps 16 ch). TUNING = NORMAL for free choice.</t>
         </is>
       </c>
     </row>
@@ -2801,14 +3465,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>To set with RF off, boot Standby: with power OFF, briefly press [AUDIO]+[FREQ] together — boots showing “rf OFF”.</t>
+          <t>Flip to XMIT to go on air. (IFBT2.0: menu-driven colour LCD — pick the channel’s Frequency + mode within its A1/B1/C1 range.)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PORTABLE RECEIVER  -  SRc / SRc5P (2-ch slot receiver)</t>
+          <t>PORTABLE RECEIVER  -  IFBlue IFBR1C / IFBR1B (belt-pack)</t>
         </is>
       </c>
     </row>
@@ -2847,7 +3511,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>SRc / SRc5P (2-ch slot receiver)</t>
+          <t>IFBlue IFBR1C / IFBR1B (belt-pack)</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -2855,7 +3519,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Press [MENU/SEL] to open setup; pick the receiver (1 or 2).</t>
+          <t>Press [FREQ] to show the receiver frequency in MHz.</t>
         </is>
       </c>
     </row>
@@ -2865,7 +3529,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Hold [MENU/SEL] + [UP]/[DOWN] to step the frequency (or use SCAN, then set).</t>
+          <t>[UP]/[DOWN] to the assigned MHz (25 or 100 kHz steps; VHF 175 kHz). [FREQ]+[UP]/[DOWN] jumps 1 MHz.</t>
         </is>
       </c>
     </row>
@@ -2875,7 +3539,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Then trigger IR SYNC to copy the receiver’s freq to the transmitter.</t>
+          <t>Store it to one of the 10 presets; [UP]/[DOWN] then scrolls saved freqs on the fly. (IFBR1C tunes the same way in a tinier body.)</t>
         </is>
       </c>
     </row>
@@ -2886,108 +3550,111 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Boot in STANDBY (RF off): with power OFF, briefly press [AUDIO]+[FREQ] together — powers up showing “rf OFF”. Set the freq, then leave Standby to transmit.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>50 / 100 / 250 mW (941 variants: 50/100). Set from OFF: hold [UP], press [AUDIO]+[FREQ] together -&gt; step to the Pr screen ([AUDIO]/[FREQ]) -&gt; [▲▼] to pick -&gt; [AUDIO]+[FREQ] to exit, then power on.</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  RX and TX must share the tuning range (A1/B1/C1 or VHF) or it can’t tune there.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Hearing nothing? Check COMPAT mode and the pilot tone — not just the frequency.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  If TX and RX blocks differ, they will never link.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Spacing defaults to 100 kHz — set Channel Spacing = 25 kHz (setup menu / LectroRM) to reach .025 / .050 / .075 assignments. Hex is just a display format.</t>
+          <t>•  IFBT4 frequency changes only in TUNE, not XMIT.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  Blocks run past TV-band UHF — Block 944 (legacy, 944.100–951.900) and current -941 variants (941.525–951.975) = the STL band; same tuning drill.</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>IFBT4 manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3416/IFBT4man_ALL.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>IFBR1B manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3419/IFBR1b_man.pdf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>SRc
-        manual</t>
+          <t>IFBT2.0 product page</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>https://lectrosonics.com/wp-content/uploads/filr/3382/SRc5P_SRc_ALL_man.pdf</t>
+          <t>https://lectrosonics.com/product/ifbt2-0/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="15">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="C32:E32"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3000,14 +3667,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lectrosonics L-Series wideband</t>
+          <t>Lectrosonics Duet (M2T / M2Ra)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Digital Hybrid UHF · spans 3 legacy blocks · portable receiver shown</t>
+          <t>Digital UHF IEM / IFB · the bodypack IS the portable receiver</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3693,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>FREE-TUNE WITHIN BLOCK</t>
+          <t>FREE-TUNE TO ANY MHz</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3705,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>100 kHz default — set Step Size = 25 kHz</t>
+          <t>25 kHz</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3717,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>A1 470.100–537.575 · B1 537.600–607.950 (US TX; RX tunes to 614.3) · C1 614.400–691.175 (each unit covers one 3-block range)</t>
+          <t>A1B1 470.100–607.975 (NA) · B1C1 version 537–691 — the unit’s range must cover the assigned MHz</t>
         </is>
       </c>
     </row>
@@ -3060,16 +3727,12 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>TX and RX ranges must overlap on the assigned MHz (A1 / B1 / C1 spans). Step Size must match on both ends — same rule as the block-units card, wider hardware.</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TRANSMITTER  -  LT / LMb / SMWB / SMDWB (wideband bodypacks)</t>
+          <t>TRANSMITTER  -  M2T (half-rack TX — two carriers, two audio ch each)</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3771,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>LT / LMb / SMWB / SMDWB (wideband bodypacks)</t>
+          <t>M2T (half-rack TX — two carriers, two audio ch each)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -3116,7 +3779,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Power on in Standby Mode: short-press the power button, releasing before the countdown reaches 3 — RF stays off (“Standby” in the Main Window) while you tune.</t>
+          <t>[Menu] -&gt; RF Tuning -&gt; pick the carrier (each of the two carriers tunes separately); [UP]/[DOWN] in 25 kHz steps; confirm.</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3789,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Menu -&gt; StepSize: set 25 kHz. Then Frequency: [UP]/[DOWN] to the assigned MHz.</t>
+          <t>RF Enable/Level: keep the carrier off while tuning; set the power level per carrier.</t>
         </is>
       </c>
     </row>
@@ -3136,14 +3799,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rf On from the Main / Power menu once confirmed — or IR-sync from the LR first, then enable RF.</t>
+          <t>Or drive the whole rack from Wireless Designer (USB / Ethernet) — freq, names, levels.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PORTABLE RECEIVER  -  LR (camera-mount receiver)</t>
+          <t>PORTABLE RECEIVER  -  M2Ra (belt-pack stereo receiver)</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3845,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>LR (camera-mount receiver)</t>
+          <t>M2Ra (belt-pack stereo receiver)</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -3190,7 +3853,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>[MENU/SEL] -&gt; set Step Size = 25 kHz, then open Frequency (or run SmartTune to scan for clear air).</t>
+          <t>Open the menu and tune to the assigned MHz (25 kHz steps) — or run SmartTune to scan on-site RF.</t>
         </is>
       </c>
     </row>
@@ -3200,66 +3863,59 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Dial the same assigned MHz; confirm on the LCD. 3Trigger IR sync at the transmitter (RX -&gt; TX) — it carries frequency, step size and compat mode in one go.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+          <t>2-way IR sync: hold the M2Ra to the M2T’s IR port — settings and scan data transfer between units (RX -&gt; TX works).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>If the rig uses a FlexList, pick the feed by name instead of dialing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>RF POWER &amp; SAFE POWER-ON</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Power the LT / LMb on in Standby Mode (RF off) and do all tuning there; turn Rf On from the Main / Power menu once set. AutoOn in the Power menu controls whether RF comes up at boot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>LT: [MENU/SEL] -&gt; TxPower -&gt; [▲▼] 50 / 100 mW -&gt; [MENU/SEL]. SMWB/SMDWB, same path: 25 / 50 / 100 mW. LMb: fixed 50 mW — no menu.</t>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Not the IFB card: Duet is the digital stereo IEM system. The M2Ra’s IFB / D2 / HDM compat modes let it stand in for an IFB R1a or D-Squared receiver — set the mode to match the TX.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>•  Reports list these as “Lectrosonics 3 Block A1 / B1” — the wideband LT / LR / SMWB family (SMWB/SMDWB tune the same way; “Nu Hybrid” on a report = these in Digital Hybrid compat), not the single-block SMV card.</t>
+          <t>•  Two independent carriers per M2T half-rack — confirm which carrier you’re tuning before you dial.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  Step Size left at 100 kHz silently hides .025 / .050 / .075 assignments — set 25 kHz on both TX and RX.</t>
+          <t>•  A1B1 vs B1C1 hardware versions — the assigned MHz must sit inside the unit’s range.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>•  Compat mode (Digital Hybrid / 100 / 200 / IFB / Mode 3…) must match the receiver or no audio.</t>
+          <t>•  M2Ra IFB compat mode is mono only.</t>
         </is>
       </c>
     </row>
@@ -3270,25 +3926,421 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>M2T manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3163/M2Tman_ALL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>M2Ra manual</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3426/M2Raman.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B23:E23"/>
+  <mergeCells count="14">
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B6:E6"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lectrosonics D Squared (DBSM / DSQD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pure digital · DBSM/DBSMD pack TX · DSQD rack / DSR4 slot RX</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>How to reach any MHz</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FREE-TUNE WITHIN BLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tuning step</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>25 kHz — always; no Step Size setting to trip on</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Range / band</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>US DBSM(D)-A1B1 470.100–607.950 · DSQD/DSR4 tune 470.1–614.375 (NA locale blocks 608–614)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Matching TX &lt;-&gt; RX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TRANSMITTER  -  DBSM / DBSMD (membrane keypad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>DBSM / DBSMD (membrane keypad)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Short-press the power button = Standby (RF off, indicator blinks) — do all tuning here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TopMenu ▸ Xmit ▸ Freq; [MENU/SEL] toggles the MHz / kHz fields; [▲▼] steps 1 MHz / 25 kHz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Enable RF with a long press through the 3-count (or Xmit ▸ Rf On? Yes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PORTABLE RECEIVER  -  DSQD (rack) / DSR4 (4-ch slot receiver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Portable Receiver</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>DSQD (rack) / DSR4 (4-ch slot receiver)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>RF Setup ▸ RF Frequency ([MENU/SEL] + [▲▼]); or Smart Tune / Frequency Scan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>IR Sync &amp; Encryption ▸ Sync Settings -&gt; SEND FREQ (or SEND ALL) -&gt; pick channel 1–4 -&gt; GO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Hold the DBSM’s IR port to the receiver — the TX has no sync menu; it just listens -&gt; “SUCCESS”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RF POWER &amp; SAFE POWER-ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Encryption key-type mismatch = RF meters but no audio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Never set DSQD/DSR4 channels 1+3 or 2+4 to the same frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>•  HDM = 2 mW only — range-check the walk before committing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>•  Exit the DSQD setup screen before powering down or settings aren’t saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>•  DCHT camera-hop TX is family: wideband 470.1–607.950, 25 kHz, Xmit ▸ Freq; pairs with DCHR (native DCHX mode) or DSQD (fw ≥ 1.04); 10 / 25 / 50 mW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>DBSM/DBSMD manual</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/1940/DBSM_man_ALL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>DSQD manual</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3315/DSQDman.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>DSR4 manual</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>https://www.lectrosonics.com/wp-content/uploads/filr/3278/DSR4man.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>DCHT manual</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>https://lectrosonics.com/wp-content/uploads/filr/3297/DCHT_man_ALL.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A34:B34"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3307,14 +4359,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lectrosonics IFB (IFBlue)</t>
+          <t>Sennheiser evolution G3 / G4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Block UHF/VHF IFB — talent &amp; crew cue feeds · portable receiver shown</t>
+          <t>Analog UHF · portable (camera) receiver shown</t>
         </is>
       </c>
     </row>
@@ -3333,7 +4385,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>FREE-TUNE WITHIN BLOCK</t>
+          <t>FREE-TUNE TO ANY MHz</t>
         </is>
       </c>
     </row>
@@ -3345,7 +4397,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>25 / 100 kHz (VHF 175 kHz)</t>
+          <t>25 kHz</t>
         </is>
       </c>
     </row>
@@ -3357,7 +4409,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Fixed ~75 MHz range; RX &amp; TX ranges must match (A1 470–537, B1 537–614, C1 614–692; VHF 174–216; “-941” 941.5–952)</t>
+          <t>Tune only inside the unit’s band letter (A 516–558, G 566–608, Aw+ 470–558…)</t>
         </is>
       </c>
     </row>
@@ -3367,16 +4419,12 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>No sync. Set the same MHz on TX and RX, keep both in the same compatibility mode, and make sure the RX range covers the TX frequency. A pilot tone keeps the RX muted until it sees a valid signal.</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TRANSMITTER  -  IFBT4 / IFBT2.0 (or any Lectro DH TX in IFB mode)</t>
+          <t>TRANSMITTER  -  SK / SKM (bodypack / handheld)</t>
         </is>
       </c>
     </row>
@@ -3415,7 +4463,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>IFBT4 / IFBT2.0 (or any Lectro DH TX in IFB mode)</t>
+          <t>SK / SKM (bodypack / handheld)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -3423,7 +4471,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>IFBT4: set the switch to TUNE (RF off — freq changes only in TUNE). Set COMPAT to match the RX (IFB is the default).</t>
+          <t>Press [SET] -&gt; Advanced -&gt; Tune -&gt; [SET] (navigate with [UP]/[DOWN] + [SET]). Unit switches to channel 1 of user bank U1 (U1–U6); TX RF is deactivated while in Tune.</t>
         </is>
       </c>
     </row>
@@ -3433,7 +4481,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Press [MENU] to the Frequency window; [UP]/[DOWN] to the assigned MHz ([MENU]+[UP]/[DOWN] jumps 16 ch). TUNING = NORMAL for free choice.</t>
+          <t>[UP]/[DOWN] to dial the assigned MHz (25 kHz steps; hold to scroll). [SET] to store.</t>
         </is>
       </c>
     </row>
@@ -3443,14 +4491,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Flip to XMIT to go on air. (IFBT2.0: menu-driven colour LCD — pick the channel’s Frequency + mode within its A1/B1/C1 range.)</t>
+          <t>[ESC] back to home; confirm the MHz on screen.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PORTABLE RECEIVER  -  IFBlue IFBR1C / IFBR1B (belt-pack)</t>
+          <t>PORTABLE RECEIVER  -  EK 100 G3 / G4 (camera receiver)</t>
         </is>
       </c>
     </row>
@@ -3489,7 +4537,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>IFBlue IFBR1C / IFBR1B (belt-pack)</t>
+          <t>EK 100 G3 / G4 (camera receiver)</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -3497,7 +4545,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Press [FREQ] to show the receiver frequency in MHz.</t>
+          <t>Press [SET] -&gt; Advanced -&gt; Tune -&gt; [SET] (switches to channel 1 of bank U1).</t>
         </is>
       </c>
     </row>
@@ -3507,7 +4555,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>[UP]/[DOWN] to the assigned MHz (25 or 100 kHz steps; VHF 175 kHz). [FREQ]+[UP]/[DOWN] jumps 1 MHz.</t>
+          <t>[UP]/[DOWN] to the same MHz; [SET] to store.</t>
         </is>
       </c>
     </row>
@@ -3517,7 +4565,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Store it to one of the 10 presets; [UP]/[DOWN] then scrolls saved freqs on the fly. (IFBR1C tunes the same way in a tinier body.)</t>
+          <t>Or set the RX here, then [SYNC] the transmitter to it via IR.</t>
         </is>
       </c>
     </row>
@@ -3528,1022 +4576,92 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Set the IFBT4 switch to TUNE — RF is off (a blinking “T” shows) and the freq can only be changed here. Flip to XMIT once set.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>IFBT4: fixed ≈250 mW. IFBT2.0: [MENU/SEL] -&gt; RF ENABLE/LEVEL -&gt; [SEL] per carrier -&gt; [▲▼] 10 / 25 / 50 / 100 / 250 mW; leave the setup screen before power-down or it won’t save.</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  RX and TX must be the same band letter, or they can’t meet on frequency.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  RX and TX must share the tuning range (A1/B1/C1 or VHF) or it can’t tune there.</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  G3 and G4 tune identically. Reports often lump G2 in too — same family drill, but verify menu names on older G2 units at the table.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Hearing nothing? Check COMPAT mode and the pilot tone — not just the frequency.</t>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  IFBT4 frequency changes only in TUNE, not XMIT.</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ew G4 system manual</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>https://docs.cloud.sennheiser.com/en-us/ew-g4/ew-g4_bedienungsanleitung_12_2025_en.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SK 500 G3 manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2025/https://assets.sennheiser.com/global-downloads/file/10828/SK_500_G3_Manual_12_2016_EN.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>EK 100 G3 manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2021/https://assets.sennheiser.com/global-downloads/file/6358/EK_100_G3_Manual_12_2016_EN.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="14">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Lectrosonics Duet (M2T / M2Ra)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Digital UHF IEM / IFB · the bodypack IS the portable receiver</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>How to reach any MHz</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FREE-TUNE TO ANY MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tuning step</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>25 kHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Range / band</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>A1B1 470.100–607.975 (NA) · B1C1 version 537–691 — the unit’s range must cover the assigned MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Matching TX &lt;-&gt; RX</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TRANSMITTER  -  M2T (half-rack TX — two carriers, two audio ch each)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Transmitter</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>M2T (half-rack TX — two carriers, two audio ch each)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>[Menu] -&gt; RF Tuning -&gt; pick the carrier (each of the two carriers tunes separately); [UP]/[DOWN] in 25 kHz steps; confirm. 2RF Enable/Level: keep the carrier off while tuning; set the power level per carrier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Or drive the whole rack from Wireless Designer (USB / Ethernet) — freq, names, levels.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>PORTABLE RECEIVER  -  M2Ra (belt-pack stereo receiver)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Portable Receiver</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>M2Ra (belt-pack stereo receiver)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Open the menu and tune to the assigned MHz (25 kHz steps) — or run SmartTune to scan on-site RF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>2-way IR sync: hold the M2Ra to the M2T’s IR port — settings and scan data transfer between units (RX -&gt; TX works).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>If the rig uses a FlexList, pick the feed by name instead of dialing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>RF POWER &amp; SAFE POWER-ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>The RF Enable/Level menu keeps each carrier OFF until you explicitly enable it — tune first, enable second. Same habit as the SMV standby boot, just menu-driven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[MENU/SEL] -&gt; RF ENABLE/LEVEL -&gt; [SEL] steps carrier/field -&gt; [▲▼] to enable and set 10 / 25 / 50 mW per carrier -&gt; [BACK].</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>•  Not the IFB card: Duet is the digital stereo IEM system. The M2Ra’s IFB / D2 / HDM compat modes let it stand in for an IFB R1a or D-Squared receiver — set the mode to match the TX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  Two independent carriers per M2T half-rack — confirm which carrier you’re tuning before you dial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  A1B1 vs B1C1 hardware versions — the assigned MHz must sit inside the unit’s range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  M2Ra IFB compat mode is mono only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Lectrosonics D Squared (DBSM / DSQD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Pure digital · DBSM/DBSMD pack TX · DSQD rack / DSR4 slot RX</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>How to reach any MHz</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FREE-TUNE WITHIN BLOCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tuning step</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>25 kHz — always; no Step Size setting to trip on</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Range / band</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>US DBSM(D)-A1B1 470.100–607.950 · DSQD/DSR4 tune 470.1–614.375 (NA locale blocks 608–614)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Matching TX &lt;-&gt; RX</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Compat modes must match end-to-end (D2 vs HDM; DSQD/DSR4 also decode Duet CH1/CH2 and Hybrid modes). Wireless Designer drives the receiver; the TX is reached only via IR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TRANSMITTER  -  DBSM / DBSMD (membrane keypad)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Transmitter</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>DBSM / DBSMD (membrane keypad)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Short-press the power button = Standby (RF off, indicator blinks) — do all tuning here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>TopMenu ▸ Xmit ▸ Freq; [MENU/SEL] toggles the MHz / kHz fields; [▲▼] steps 1 MHz / 25 kHz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Enable RF with a long press through the 3-count (or Xmit ▸ Rf On? Yes).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>PORTABLE RECEIVER  -  DSQD (rack) / DSR4 (4-ch slot receiver)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Portable Receiver</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>DSQD (rack) / DSR4 (4-ch slot receiver)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>RF Setup ▸ RF Frequency ([MENU/SEL] + [▲▼]); or Smart Tune / Frequency Scan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>IR Sync &amp; Encryption ▸ Sync Settings -&gt; SEND FREQ (or SEND ALL) -&gt; pick channel 1–4 -&gt; GO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Hold the DBSM’s IR port to the receiver — the TX has no sync menu; it just listens -&gt; “SUCCESS”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>RF POWER &amp; SAFE POWER-ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Built into the power button: short press = Standby (RF off); releasing a long press before the countdown reaches 3 also boots RF-off. Full 3-count (or Xmit ▸ Rf On?) to radiate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Xmit ▸ TxPower: 10 / 25 / 50 mW, or HDM = 2 mW high-density mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  Encryption key-type mismatch = RF meters but no audio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Never set DSQD/DSR4 channels 1+3 or 2+4 to the same frequency.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  HDM = 2 mW only — range-check the walk before committing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>•  Exit the DSQD setup screen before powering down or settings aren’t saved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>•  DCHT camera-hop TX is family: wideband 470.1–607.950, 25 kHz, Xmit ▸ Freq; pairs with DCHR (native DCHX mode) or DSQD (fw ≥ 1.04); 10 / 25 / 50 mW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sennheiser evolution G3 / G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Analog UHF · portable (camera) receiver shown</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>How to reach any MHz</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FREE-TUNE TO ANY MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tuning step</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>25 kHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Range / band</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Tune only inside the unit’s band letter (A 516–558, G 566–608, Aw+ 470–558…)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Matching TX &lt;-&gt; RX</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Bank presets (1–20) only hold fixed compatible channels — use Tune (bank U) to reach an arbitrary freq.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TRANSMITTER  -  SK / SKM (bodypack / handheld)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Transmitter</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>SK / SKM (bodypack / handheld)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Press [SET] -&gt; Advanced -&gt; Tune -&gt; [SET] (navigate with [UP]/[DOWN] + [SET]). Unit switches to channel 1 of user bank U1 (U1–U6); TX RF is deactivated while in Tune.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>[UP]/[DOWN] to dial the assigned MHz (25 kHz steps; hold to scroll). [SET] to store.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>PORTABLE RECEIVER  -  EK 100 G3 / G4 (camera receiver)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Portable Receiver</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>EK 100 G3 / G4 (camera receiver)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Press [SET] -&gt; Advanced -&gt; Tune -&gt; [SET] (switches to channel 1 of bank U1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>[UP]/[DOWN] to the same MHz; [SET] to store.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Or set the RX here, then [SYNC] the transmitter to it via IR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>RF POWER &amp; SAFE POWER-ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Entering Tune deactivates the TX RF while you dial (“the RF signal is deactivated”, per manual) — tune before approaching the rig. Where fitted, set the mute switch function to RF Mute (menu: Mute Mode) for a hard mute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>G4 300/500: 10 / 30 / 50 mW (Low/Standard/High), Advanced ▸ RF Power. G3 300/500: 10 / 30 mW (Low/Standard) only. 100-series: fixed, max 30 mW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>•  RX and TX must be the same band letter, or they can’t meet on frequency.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  G3 and G4 tune identically. Reports often lump G2 in too — same family drill, but verify menu names on older G2 units at the table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4627,11 +4745,7 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>No sync — match the channel number on TX and RX from the chart. Running 2+ channels on one site needs intermod-checked channel groups (Comtek’s chart / frequency software).</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -4788,84 +4902,1115 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>No RF-off standby — the BST radiates once powered. Set the channel before powering near the rig (or before the antenna goes on), then use the display-off lockout to freeze tuning.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>BST-25: fixed, set for 100 mW (FCC Parts 22/74/90). BST 75-216 = compact 10-channel “Mini Base Station” with selectable power; M-216 is the belt-pack TX.</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  VHF 216–217 — completely outside UHF TV coordination; it appears on reports as a channel number, not a free MHz.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Narrow vs hi-fi companded are different channel sets — a mismatch passes RF but sounds wrong.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  VHF 216–217 — completely outside UHF TV coordination; it appears on reports as a channel number, not a free MHz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Narrow vs hi-fi companded are different channel sets — a mismatch passes RF but sounds wrong.</t>
+          <t>•  Display disabled = tuning locked (the rear LOCK OUT switch does the same). Re-enable to change channels.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  Display disabled = tuning locked (the rear LOCK OUT switch does the same). Re-enable to change channels.</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>BST 25-216 manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://img1.wsimg.com/blobby/go/414496dc-67ac-402c-ac0d-00342b1b241d/downloads/BST%2025-216%20Manual.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>PR-216 manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://img1.wsimg.com/blobby/go/414496dc-67ac-402c-ac0d-00342b1b241d/downloads/PR-216%20Manual.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="13">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sound Devices Astral (A20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Digital wideband (SpectraBand) · portable receiver shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>How to reach any MHz</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FREE-TUNE TO ANY MHz</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tuning step</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>25 kHz (off the sub-channel grid is OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Range / band</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>SpectraBand 470–1525 MHz (A20-TX &amp; A20-RX reach down to 169; HH/Mini start at 470) — region/license-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Matching TX &lt;-&gt; RX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TRANSMITTER  -  Astral TX / HH (display) · Mini (app)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Astral TX / HH (display) · Mini (app)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Astral TX / HH: open the menu -&gt; Frequency. (There is no Country menu on the unit — region limits are set automatically via the A20-Remote app or an Astral receiver.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Dial the assigned MHz and confirm; turn RF on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Astral Mini (no screen): set frequency from the A20-Remote app, or push it from the receiver / Nexus over NexLink.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PORTABLE RECEIVER  -  A20-RX / ARX2 (2-ch portable receiver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Portable Receiver</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>A20-RX / ARX2 (2-ch portable receiver)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Press [◀] or [▶] to select a channel (single-channel view); press the centre [ENTER] to open its menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Go to Frequency -&gt; [ENTER]; [◀]/[▶] to set the assigned MHz; [ENTER] to confirm. (An * just means it’s off the preset sub-channel grid — fine.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Set the transmitter to the same MHz (on-unit, app, or NexLink). Tip: AutoAssign scans a chosen band and fills both channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RF POWER &amp; SAFE POWER-ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Available freqs are country-gated (set via A20-Remote / receiver, plus any FA license code); restricted bands stay locked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  GainForward: no gain on the transmitter — gain is set at the receiver / mixer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>•  Digital &amp; intermod-immune, but keep A20 units ≥ 400 kHz apart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>A20-TX user guide</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://cdn.sounddevices.com/wp-content/uploads/2025/04/A20-TX-User-Guide-v8.10.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>A20-RX user guide</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://cdn.sounddevices.com/wp-content/uploads/2024/11/A20-RX-v8.00-User-Guide.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Frequencies by country</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sounddevices.com/available-frequencies/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zaxcom (ZMT4.5 / URX100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pure digital · ZaxNet 2.4 GHz remote control · no IR anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>How to reach any MHz</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FREE-TUNE TO ANY MHz</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tuning step</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>100 kHz (0.1 MHz per INC/DEC press)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Range / band</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ZMT4.5 512–608 (Blocks 20–23) · ZMT4.6 578–698 · VTX1 VHF 192–217 (FM 215–216.975 = Comtek-compatible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Matching TX &lt;-&gt; RX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TRANSMITTER  -  ZMT4.5 (micro bodypack TX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>ZMT4.5 (micro bodypack TX)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>From Home press [MENU] to “UHF Transmit Frequency Set” (TXFREQ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>[INC]/[DEC]: short press = 0.1 MHz, hold = 0.5 MHz jumps. Direct dial — no groups, no banks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Keys locked? Hold [MENU] + press [INC] ×5 to unlock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PORTABLE RECEIVER  -  URX100 (portable confidence RX; bags run Nova/MRX214)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Portable Receiver</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>URX100 (portable confidence RX; bags run Nova/MRX214)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>[MENU] to “Frequency Select”; [CH UP]/[CH DOWN] tune in 0.1 MHz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Or Frequency Scan -&gt; accept the suggested clear freq with [CH UP].</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Modulation must match the TX — URX100 decodes ZHD96 / XR / MONO but not ZHD48 (ZHD48 needs a current MRX214).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RF POWER &amp; SAFE POWER-ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Modulation mode (ZHD48 / ZHD96 / XR) must match TX↔RX — changing it forces a reboot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  ZHD48 occupies ~50 kHz and can sit 100 kHz apart — expect tighter packing than analog on the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>•  ZaxNet (2.403–2.475 GHz) is a real on-site emitter — coordinate it too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>•  TRXCL5 camera link tunes the same way (INC/DEC, 100 kHz): US 512–607.9 up to 100 mW (+ 614.1–615.9 / 653.1–662.9 at 20 mW); power 25 / 50 / 100 mW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ZMT4/4.5 manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://zaxcom.com/wp-content/uploads/2022/01/Zaxcom_ZMT4_Manual_April_2021.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>URX100 manual</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://zaxcom.com/wp-content/uploads/2019/05/Zaxcom_URX100_Manual_August_2019.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>VTX1 manual</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>https://zaxcom.com/wp-content/uploads/2025/08/Zaxcom_VTX1_July_2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TRXCL5 manual</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>https://zaxcom.com/wp-content/uploads/2023/06/Zaxcom_TRXCL5_Manual_August-2022-1.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A34:B34"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Shure Wireless Workbench (WWB 6 &amp; 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Software · making WWB accept coordinator-assigned frequencies · nothing on this card transmits</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>How to reach any MHz</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>SOFTWARE — CALC ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tuning step</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>profiles: Robust · Standard · More Frequencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Range / band</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>applies only to the WWB calculator on your laptop — it changes nothing on any transmitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Matching TX &lt;-&gt; RX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WWB 6  -  WWB 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Wwb 6</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>WWB 6</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Frequency Coordination tab -&gt; click the device-type group header (its text shows the active profile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Right sidebar -&gt; Compatibility tab -&gt; Compatibility Profile drop-down -&gt; More Frequencies (try Standard first if you only need a little slack).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Keep the assigned freqs; [Calculate] — the warnings should clear. (Spacing numbers live in Tools ▸ Equipment Profiles.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>WWB 7  -  WWB 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Wwb 7</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>WWB 7</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Frequency coordination workspace -&gt; click the device header (dark grey bar); [Ctrl]-click to select several.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Compatibility tab -&gt; profile drop-down -&gt; More frequencies (or Standard). Fine sliders: Channel / Intermod spacing (2- &amp; 3-TX); [Revert] undoes, [Save] keeps a modified profile (*).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>[Calculate]. Global default: Preferences ▸ Coordination ▸ Compatibility -&gt; double-click the model’s Coordination Preference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RF POWER &amp; SAFE POWER-ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  “3TO”-style warnings are WWB’s own 2- and 3-transmitter third-order intermod spacing rules — a margin policy, not a verdict on the event plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Set the profile per device type — relax only the types you were handed frequencies for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>•  If WWB still refuses one specific assigned frequency, don’t nudge it to a nearby number — call coordination; the digits are load-bearing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>WWB help — Adjust Compatibility Settings</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://content-files.shure.com/Pubs/WWB/en-US/en-US/adjust-compatibility-settings.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>WWB6 compatibility profiles (Shure)</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shure.com/en-US/insights/shure-wireless-workbench-6-compatibility-profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>WWB help — Specify a Frequency</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://content-files.shure.com/Pubs/WWB/en-US/en-US/specify-a-frequency-for-a-channel.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4884,14 +6029,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sound Devices Astral (A20)</t>
+          <t>Teradek Bolt / Ranger (wireless video)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Digital wideband (SpectraBand) · portable receiver shown</t>
+          <t>5 / 6 GHz zero-delay video · lock it to one channel so it can’t hop</t>
         </is>
       </c>
     </row>
@@ -4910,7 +6055,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>FREE-TUNE TO ANY MHz</t>
+          <t>LOCK TO ONE CHANNEL</t>
         </is>
       </c>
     </row>
@@ -4922,7 +6067,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>25 kHz (off the sub-channel grid is OK)</t>
+          <t>20 MHz per link (factory default is 40 MHz — twice the footprint)</t>
         </is>
       </c>
     </row>
@@ -4934,7 +6079,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SpectraBand 470–1525 MHz (A20-TX &amp; A20-RX reach down to 169; HH/Mini start at 470) — region/license-gated</t>
+          <t>5 GHz U-NII-1/2/3 · 6 GHz U-NII-5 5.925–6.425 (Bolt 6 · Bolt 4K LT-HDMI · Ranger Mk II/Micro)</t>
         </is>
       </c>
     </row>
@@ -4944,16 +6089,12 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>No IR sync. TX and RX must share the same frequency + modulation; match by hand, via A20-Remote, or push over NexLink (the screenless Mini must be set this way).</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TRANSMITTER  -  Astral TX / HH (display) · Mini (app)</t>
+          <t>LOCK THE FREQUENCY  -  Same steps on TX and RX</t>
         </is>
       </c>
     </row>
@@ -4987,12 +6128,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Transmitter</t>
+          <t>Lock The Frequency</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Astral TX / HH (display) · Mini (app)</t>
+          <t>Same steps on TX and RX</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -5000,7 +6141,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Astral TX / HH: open the menu -&gt; Frequency. (There is no Country menu on the unit — region limits are set automatically via the A20-Remote app or an Astral receiver.)</t>
+          <t>[Menu] -&gt; Wireless Settings -&gt; Enable Fixed Frequency — on both TX and RX (“bypasses any automatic frequency switching logic”).</t>
         </is>
       </c>
     </row>
@@ -5010,7 +6151,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Dial the assigned MHz and confirm; turn RF on.</t>
+          <t>Then Wireless Settings ▸ Frequencies: select only the assigned channel. If you skip this, Bolt silently defaults to the lowest frequency in the list.</t>
         </is>
       </c>
     </row>
@@ -5020,14 +6161,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Astral Mini (no screen): set frequency from the A20-Remote app, or push it from the receiver / Nexus over NexLink.</t>
+          <t>Fixed mode offers non-DFS channels only — if your assignment is a DFS channel, the unit cannot lock there; call coordination.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PORTABLE RECEIVER  -  A20-RX / ARX2 (2-ch portable receiver)</t>
+          <t>LOCK 20 MHz + BAND  -  Same steps on TX and RX</t>
         </is>
       </c>
     </row>
@@ -5061,12 +6202,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Portable Receiver</t>
+          <t>Lock 20 Mhz + Band</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>A20-RX / ARX2 (2-ch portable receiver)</t>
+          <t>Same steps on TX and RX</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -5074,7 +6215,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Press [◀] or [▶] to select a channel (single-channel view); press the centre [ENTER] to open its menu.</t>
+          <t>[Menu] -&gt; Wireless Settings -&gt; Bandwidth -&gt; 20MHz (default 40) — both ends must match. 20 MHz carries up to 1080p60; 4K59/60 needs 40 MHz.</t>
         </is>
       </c>
     </row>
@@ -5084,7 +6225,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Go to Frequency -&gt; [ENTER]; [◀]/[▶] to set the assigned MHz; [ENTER] to confirm. (An * just means it’s off the preset sub-channel grid — fine.)</t>
+          <t>6 GHz-capable units: Wireless Settings ▸ Band -&gt; 5GHz or 6GHz per the assignment — both ends; hopping never spans bands.</t>
         </is>
       </c>
     </row>
@@ -5094,7 +6235,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Set the transmitter to the same MHz (on-unit, app, or NexLink). Tip: AutoAssign scans a chosen band and fills both channels.</t>
+          <t>Sanity-check with the Spectrum Analyzer (RX front panel / Bolt app). Changed the Region setting? Re-pair TX and RX.</t>
         </is>
       </c>
     </row>
@@ -5105,123 +6246,126 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Use the menu RF Off toggle (or set RF Power = Off on the Mini) so it’s powered but not radiating; set the freq; then RF On.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>A20-TX/Mini 2 / 10 / 20 / 40 mW (40 needs the Extra RF Power enable); HH adds 40 “Very High” / 100 mW “Extra High”, both behind the same enable. Set on the unit, A20-Remote, or the receiver. Tip: raise Long-Range modulation before power.</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Serv / Prism / Cube are IP encoders on ordinary Wi-Fi — nothing to lock on the unit; coordinate the network instead.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Frequency, bandwidth, and band must match on both ends or the link won’t form.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  Available freqs are country-gated (set via A20-Remote / receiver, plus any FA license code); restricted bands stay locked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  GainForward: no gain on the transmitter — gain is set at the receiver / mixer.</t>
+          <t>•  See the companion 5/6 GHz channel chart card for channel ⇄ MHz mapping.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  Digital &amp; intermod-immune, but keep A20 units ≥ 400 kHz apart.</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Bolt 6 wireless configuration</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://guide.teradek.com/a/1601336-wireless-configuration</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Bolt 4K wireless configuration</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://guide.teradek.com/a/1625378-wireless-configuration</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>A20-RX user
-        guide</t>
+          <t>Bolt 6 GHz support by region</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>https://cdn.sounddevices.com/wp-content/uploads/2024/11/A20-RX-v8.00-User-Guide.pdf</t>
+          <t>https://guide.teradek.com/a/1601470-bolt-6-u-nii-5-6ghz-support-by-region</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Frequencies by country</t>
+          <t>Frequencies by region chart</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>https://www.sounddevices.com/available-frequencies/</t>
+          <t>https://guide.teradek.com/a/1589935-frequencies-by-region</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="17">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="C32:E32"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5234,14 +6378,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zaxcom (ZMT4.5 / URX100)</t>
+          <t>5 / 6 GHz Channel Chart (video &amp; Wi-Fi)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pure digital · ZaxNet 2.4 GHz remote control · no IR anywhere</t>
+          <t>Generic 20 MHz channelization · channel ⇄ center MHz · who can go to 6 GHz</t>
         </is>
       </c>
     </row>
@@ -5260,7 +6404,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>FREE-TUNE TO ANY MHz</t>
+          <t>REFERENCE CHART</t>
         </is>
       </c>
     </row>
@@ -5270,11 +6414,7 @@
           <t>Tuning step</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>100 kHz (0.1 MHz per INC/DEC press)</t>
-        </is>
-      </c>
+      <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5282,11 +6422,7 @@
           <t>Range / band</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>ZMT4.5 512–608 (Blocks 20–23) · ZMT4.6 578–698 · VTX1 VHF 192–217 (FM 215–216.975 = Comtek-compatible)</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -5294,157 +6430,215 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>No IR. Frequencies can be pushed over ZaxNet 2.4 GHz (Group Code 1–99 + Unit Code 1–200 address each pack; controller = Nova2 “TRX Frequency” or VTX1 remote menu).</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TRANSMITTER  -  ZMT4.5 (micro bodypack TX)</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>5 GHz band</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Span (MHz)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>20 MHz channels (center MHz)</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Rules</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>U-NII-1</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>5150–5250</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>36 (5180) · 40 (5200) · 44 (5220) · 48 (5240)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>No DFS — lockable</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Transmitter</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>ZMT4.5 (micro bodypack TX)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>From Home press [MENU] to “UHF Transmit Frequency Set” (TXFREQ).</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>U-NII-2A</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>5250–5350</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>52 (5260) · 56 (5280) · 60 (5300) · 64 (5320)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>DFS — radar scan, can be evicted</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>[INC]/[DEC]: short press = 0.1 MHz, hold = 0.5 MHz jumps. Direct dial — no groups, no banks.</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>U-NII-2C</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>5470–5725</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>100 (5500) · 104 · 108 · 112 · 116 · 120 · 124 · 128 · 132 · 136 · 140 · 144 (5720)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>DFS — radar scan, can be evicted</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Keys locked? Hold [MENU] + press [INC] ×5 to unlock.</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>U-NII-3</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>5725–5850</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>149 (5745) · 153 (5765) · 157 (5785) · 161 (5805) · 165 (5825)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>No DFS — lockable, but shared with venue Wi-Fi</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>PORTABLE RECEIVER  -  URX100 (portable confidence RX; bags run Nova/MRX214)</t>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>6 GHz band</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Span (MHz)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>20 MHz channels (center MHz)</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Rules</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>U-NII-5</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>5925–6425</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>1 (5955) · 5 (5975) · 9 (5995) … step +4 ch / +20 MHz … 93 (6415)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>No DFS; lower power (LPI); only band Teradek uses</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Portable Receiver</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>URX100 (portable confidence RX; bags run Nova/MRX214)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>[MENU] to “Frequency Select”; CH UP/[CH DOWN] tune in 0.1 MHz.</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>U-NII-6</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>6425–6525</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>97 (6435) – 113 (6515)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6E/7 only — no Teradek products here; venue APs may be</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Or Frequency Scan -&gt; accept the suggested clear freq with [CH UP].</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>U-NII-7</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>6525–6875</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>117 (6535) – 185 (6875)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Modulation must match the TX — URX100 decodes ZHD96 / XR / MONO but not ZHD48 (ZHD48 needs a current MRX214).</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>U-NII-8</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>6875–7125</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>189 (6895) – 233 (7115)</t>
         </is>
       </c>
     </row>
@@ -5455,85 +6649,109 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Setup ▸ “Standby Mode After Boot Up”: STANDBY (wakes on MENU press) or REMOTE STANDBY (boots RF-silent, waits for a ZaxNet WAKE from Nova2 / VTX1). Transmit ▸ Record-Only Mode kills UHF entirely. RF POWERZMT4.5 TX POWER: 10 / 50 mW. VTX1: 10 / 25 / 50 mW.</t>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Teradek fixed-frequency locks only exist in the green rows (U-NII-1, U-NII-3, U-NII-5).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>•  Modulation mode (ZHD48 / ZHD96 / XR) must match TX↔RX — changing it forces a reboot.</t>
+          <t>•  A 40 MHz link eats two adjacent 20 MHz slots — count both when charting.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  ZHD48 occupies ~50 kHz and can sit 100 kHz apart — expect tighter packing than analog on the report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  ZaxNet (2.403–2.475 GHz) is a real on-site emitter — coordinate it too.</t>
+          <t>•  Venue Wi-Fi lives in these same bands; 6 GHz (U-NII-5) is usually the cleanest room on site.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  TRXCL5 camera link tunes the same way (INC/DEC, 100 kHz): US 512–607.9 up to 100 mW (+ 614.1–615.9 / 653.1–662.9 at 20 mW); power 25 / 50 / 100 mW.</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Teradek frequencies by region</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://guide.teradek.com/a/1589935-frequencies-by-region</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Bolt 6 6 GHz support</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://guide.teradek.com/a/1601470-bolt-6-u-nii-5-6ghz-support-by-region</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>WLAN channel list (IEEE numbering)</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_WLAN_channels</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="13">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5546,14 +6764,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Shure Wireless Workbench (WWB 6 &amp; 7)</t>
+          <t>2.4 GHz Auto-Hop Mics (DJI / Rode / Hollyland)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Software · making WWB accept coordinator-assigned frequencies · nothing on this card transmits</t>
+          <t>Consumer digital mics · adaptive frequency hopping · there is no frequency to dial</t>
         </is>
       </c>
     </row>
@@ -5572,7 +6790,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SOFTWARE — CALC ONLY</t>
+          <t>CANNOT BE COORDINATED</t>
         </is>
       </c>
     </row>
@@ -5584,7 +6802,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>profiles: Robust · Standard · More Frequencies</t>
+          <t>none — the radio picks its own hops, continuously</t>
         </is>
       </c>
     </row>
@@ -5596,7 +6814,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>applies only to the WWB calculator on your laptop — it changes nothing on any transmitter</t>
+          <t>2.400–2.4835 GHz ISM (DJI Mic 3 can also use 5.1–5.8 GHz)</t>
         </is>
       </c>
     </row>
@@ -5611,7 +6829,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>WWB 6  -  WWB 6</t>
+          <t>WHAT THEY ARE  -  All 2.4 GHz ISM, all auto-hop</t>
         </is>
       </c>
     </row>
@@ -5645,12 +6863,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Wwb 6</t>
+          <t>What They Are</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>WWB 6</t>
+          <t>All 2.4 GHz ISM, all auto-hop</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -5658,7 +6876,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Frequency Coordination tab -&gt; click the device-type group header (its text shows the active profile).</t>
+          <t>DJI Mic / Mic 2 / Mic Mini: 2.400–2.4835 GHz, GFSK, &lt; 20 dBm EIRP (Mic 3 adds 5.1–5.8 GHz).</t>
         </is>
       </c>
     </row>
@@ -5668,7 +6886,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Right sidebar -&gt; Compatibility tab -&gt; Compatibility Profile drop-down -&gt; More Frequencies (try Standard first if you only need a little slack).</t>
+          <t>Rode Wireless GO II / PRO / ME: “Series IV” 2.4 GHz digital, 128-bit encryption, auto-pairing.</t>
         </is>
       </c>
     </row>
@@ -5678,14 +6896,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Keep the assigned freqs; [Calculate] — the warnings should clear. (Spacing numbers live in Tools ▸ Equipment Profiles.)</t>
+          <t>Hollyland Lark M2 / Max: 2.4 GHz adaptive frequency hopping, &lt; 20 dBm EIRP.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>WWB 7  -  WWB 7</t>
+          <t>WHAT TO TELL THE CREW  -  Kindly, at the check-in table</t>
         </is>
       </c>
     </row>
@@ -5719,12 +6937,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Wwb 7</t>
+          <t>What To Tell The Crew</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>WWB 7</t>
+          <t>Kindly, at the check-in table</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -5732,7 +6950,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Frequency coordination workspace -&gt; click the device header (dark grey bar); [Ctrl]-click to select several.</t>
+          <t>These can’t take an assigned frequency — that’s the design, not a setting you’re missing.</t>
         </is>
       </c>
     </row>
@@ -5742,7 +6960,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Compatibility tab -&gt; profile drop-down -&gt; More frequencies (or Standard). Fine sliders: Channel / Intermod spacing (2- &amp; 3-TX); [Revert] undoes, [Save] keeps a modified profile (*).</t>
+          <t>They share 2.4 GHz with venue Wi-Fi, Bluetooth, ZaxNet, and comms — count them on the walk anyway; every one raises the noise floor.</t>
         </is>
       </c>
     </row>
@@ -5752,7 +6970,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>[Calculate]. Global default: Preferences ▸ Coordination ▸ Compatibility -&gt; double-click the model’s Coordination Preference.</t>
+          <t>Power off units that aren’t actively shooting; if reliability matters, hand them a coordinated UHF pack instead.</t>
         </is>
       </c>
     </row>
@@ -5763,90 +6981,141 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>DON’T RECALC</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Type the coordinator’s frequencies exactly (double-click the Inventory Frequency column). Relaxing the profile only makes WWB accept them — don’t generate new frequencies without asking coordination.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>TRADE-OFF</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>More Frequencies = tighter spacings: less margin against intermod products and short TX-to-RX distances. Fine when the site-wide coordination owns the plan; not a free win when you’re self-coordinating in isolation.</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Nothing on this card is field-tunable — if a crew insists their unit “has a channel setting,” it’s a pairing menu, not a frequency menu.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  DJI Mic 3 in 5 GHz mode lands in the same U-NII bands as Teradek video — see the 5/6 GHz chart card.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  “3TO”-style warnings are WWB’s own 2- and 3-transmitter third-order intermod spacing rules — a margin policy, not a verdict on the event plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Set the profile per device type — relax only the types you were handed frequencies for.</t>
+          <t>•  These are fine tools in isolation; the problem is density.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  If WWB still refuses one specific assigned frequency, don’t nudge it to a nearby number — call coordination; the digits are load-bearing.</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>DJI Mic 2 specs</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dji.com/mic-2/specs</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Rode Wireless GO II</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://rode.com/en-us/microphones/wireless/wirelessgoii</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Hollyland Lark Max specs</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hollyland.com/product/lark-max</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Lamarr FHSS patent (1942)</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>https://patents.google.com/patent/US2292387A/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Hedy Lamarr — MIT Lemelson</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>https://lemelson.mit.edu/resources/hedy-lamarr</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="19">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5859,14 +7128,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Teradek Bolt / Ranger (wireless video)</t>
+          <t>Sennheiser EW-DX</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5 / 6 GHz zero-delay video · lock it to one channel so it can’t hop</t>
+          <t>Digital UHF · no portable RX in-series — EW-DP EK is the camera option</t>
         </is>
       </c>
     </row>
@@ -5885,7 +7154,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>LOCK TO ONE CHANNEL</t>
+          <t>FREE-TUNE TO ANY MHz</t>
         </is>
       </c>
     </row>
@@ -5897,7 +7166,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>20 MHz per link (factory default is 40 MHz — twice the footprint)</t>
+          <t>fine (MHz + kHz entry; factory presets sit on a 600 kHz grid)</t>
         </is>
       </c>
     </row>
@@ -5909,7 +7178,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>5 GHz U-NII-1/2/3 · 6 GHz U-NII-5 5.925–6.425 (Bolt 6 · Bolt 4K LT-HDMI · Ranger Mk II/Micro)</t>
+          <t>US: Q1-9 470.2–550 · R1-9 520–607.8 · V5-7 941.7–959.65 (licensed STL)</t>
         </is>
       </c>
     </row>
@@ -5919,16 +7188,12 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Ranger is the special case: spans 4.9–6.0 GHz including licensed channels — enable Allow Licensed Channels + Fixed Frequency to pick one (licensed operations only).</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>LOCK THE FREQUENCY  -  Same steps on TX and RX</t>
+          <t>TRANSMITTER  -  SK / SKM(-S) (bodypack / handheld)</t>
         </is>
       </c>
     </row>
@@ -5962,12 +7227,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Lock The Frequency</t>
+          <t>Transmitter</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Same steps on TX and RX</t>
+          <t>SK / SKM(-S) (bodypack / handheld)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -5975,7 +7240,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>[Menu] -&gt; Wireless Settings -&gt; Enable Fixed Frequency — on both TX and RX (“bypasses any automatic frequency switching logic”). 2Then Wireless Settings ▸ Frequencies: select only the assigned channel. If you skip this, Bolt silently defaults to the lowest frequency in the list.</t>
+          <t>Press [SET] to open the menu -&gt; Frequency; [UP]/[DOWN] sets the MHz range -&gt; [SET] -&gt; [UP]/[DOWN] sets the kHz -&gt; [SET] to save.</t>
         </is>
       </c>
     </row>
@@ -5985,140 +7250,133 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fixed mode offers non-DFS channels only — if your assignment is a DFS channel, the unit cannot lock there; call coordination.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>LOCK 20 MHz + BAND  -  Same steps on TX and RX</t>
+          <t>Or sync from the receiver: press [CH 1]/[CH 2] on the EM 2 -&gt; [SYNC] on the receiver -&gt; short-press [SYNC] on the TX (Bluetooth LE — no IR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Keep that TX press short — holding [SYNC] &gt; 2 s enters firmware-update mode and cancels the sync.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PORTABLE RECEIVER  -  EW-DP EK (camera receiver, cross-compatible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Device</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Instruction</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Notes / Corrections</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Lock 20 Mhz + Band</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Same steps on TX and RX</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Portable Receiver</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>EW-DP EK (camera receiver, cross-compatible)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>[Menu] -&gt; Wireless Settings -&gt; Bandwidth -&gt; 20MHz (default 40) — both ends must match. 20 MHz carries up to 1080p60; 4K59/60 needs 40 MHz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>6 GHz-capable units: Wireless Settings ▸ Band -&gt; 5GHz or 6GHz per the assignment — both ends; hopping never spans bands.</t>
+          <t>[UP]/[DOWN]/[SET]/[ESC] -&gt; FREQUENCY (or AUTO SCAN / CHANNEL).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Set the assigned MHz; [SET] to save.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Sanity-check with the Spectrum Analyzer (RX front panel / Bolt app). Changed the Region setting? Re-pair TX and RX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Must be the same frequency-range variant as the TX; EW-DX extras (encryption, LD) drop off on EW-DP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>RF POWER &amp; SAFE POWER-ON</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>NO DFS LOCK</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Fixed Frequency = non-DFS only. DFS ranges (5.25–5.35 / 5.47–5.725 GHz) need a 1-minute radar scan and can be forced to vacate — don’t assign video links there.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>FOOTPRINT</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>6 GHz (U-NII-5) runs at lower allowed power than 5 GHz but has no DFS. At 20 MHz a Bolt 6 offers 36 channel choices vs 24 at 40 MHz.</t>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Enabling AES-256 (System -&gt; Link Encryption) requires re-syncing every TX.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>•  Serv / Prism / Cube are IP encoders on ordinary Wi-Fi — nothing to lock on the unit; coordinate the network instead.</t>
+          <t>•  Link Density mode needs a receiver restart; presets shift to a 300 kHz grid.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  Frequency, bandwidth, and band must match on both ends or the link won’t form.</t>
+          <t>•  TX and RX must share the frequency-range variant (Q1-9 vs R1-9…).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>•  See the companion 5/6 GHz channel chart card for channel ⇄ MHz mapping.</t>
+          <t>•  EW-D (non-DX) TXs have no display at all — set the freq on the EW-D EM (or Smart Assist app) and push with the [SYNC] buttons (BLE). Fixed 10 mW. Q1-6 = 470.2–526; “S1-7” = 606.2–662 (mostly not US-legal).</t>
         </is>
       </c>
     </row>
@@ -6132,45 +7390,89 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Frequencies by region chart</t>
+          <t>EW-D/DX/DP combined manual</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>https://guide.teradek.com/a/1589935-frequencies-by-region</t>
+          <t>https://www.sennheiser.com/globalassets/digizuite/40783-en-instruction-manual-and-frequently-asked-questions---evolution-wireless-digital-ew-d--ew-dx--ew-dp-pdf.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>EW-DX online manual</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://docs.cloud.sennheiser.com/en-us/ew-d/ew-d/manual.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Frequency ranges</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>https://docs.cloud.sennheiser.com/en-us/ew-d/ew-d/productinfo-freq-ranges.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>EW-D manual</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>https://assets.sennheiser.com/download/assets/ew-d_instruction_manual_06_2026_en.pdf/092d50fcf2f111f0b4c42e4518a8e27d?attachment=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B23:E23"/>
+  <mergeCells count="18">
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B6:E6"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B6:E6"/>
     <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="B22:E22"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6183,14 +7485,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5 / 6 GHz Channel Chart (video &amp; Wi-Fi)</t>
+          <t>Sennheiser Digital 6000</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generic 20 MHz channelization · channel ⇄ center MHz · who can go to 6 GHz</t>
+          <t>Digital UHF · portable (camera) receiver shown</t>
         </is>
       </c>
     </row>
@@ -6209,7 +7511,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>REFERENCE CHART</t>
+          <t>FREE-TUNE TO ANY MHz</t>
         </is>
       </c>
     </row>
@@ -6219,7 +7521,11 @@
           <t>Tuning step</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>25 kHz</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6227,7 +7533,11 @@
           <t>Range / band</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Up to 88–184 MHz tuning, depending on unit</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -6238,212 +7548,150 @@
       <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>5 GHz band</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Span (MHz)</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>20 MHz channels (center MHz)</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Rules</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TRANSMITTER  -  SK 6000 / SKM 6000</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>U-NII-1</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>5150–5250</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>36 (5180) · 40 (5200) · 44 (5220) · 48 (5240)</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>No DFS — lockable</t>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>U-NII-2A</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>5250–5350</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>52 (5260) · 56 (5280) · 60 (5300) · 64 (5320)</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>DFS — radar scan, can be evicted</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>SK 6000 / SKM 6000</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>On the TX, press [SET] to open the menu -&gt; Tune.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>U-NII-2C</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>5470–5725</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>100 (5500) · 104 · 108 · 112 · 116 · 120 · 124 · 128 · 132 · 136 · 140 · 144 (5720)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>DFS — radar scan, can be evicted</t>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Set the assigned MHz (25 kHz steps); confirm — saving auto-assigns it to preset U.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>U-NII-3</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>5725–5850</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>149 (5745) · 153 (5765) · 157 (5785) · 161 (5805) · 165 (5825)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>No DFS — lockable, but shared with venue Wi-Fi</t>
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Match the transmission mode (e.g. LR) to the receiver, or the link won’t form.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>6 GHz band</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Span (MHz)</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>20 MHz channels (center MHz)</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Rules</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PORTABLE RECEIVER  -  EK 6042 (2-ch camera receiver, LR)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>U-NII-5</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>5925–6425</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>1 (5955) · 5 (5975) · 9 (5995) … step +4 ch / +20 MHz … 93 (6415)</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>No DFS; lower power (LPI); only band Teradek uses</t>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>U-NII-6</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>6425–6525</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>97 (6435) – 113 (6515)</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Wi-Fi 6E/7 only — no Teradek products here; venue APs may be</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Portable Receiver</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>EK 6042 (2-ch camera receiver, LR)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Press the channel button -&gt; CH Settings -&gt; Frequency -&gt; Tune.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>U-NII-7</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>6525–6875</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>117 (6535) – 185 (6875)</t>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Set the same MHz; confirm.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>U-NII-8</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>6875–7125</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>189 (6895) – 233 (7115)</t>
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Then Sync transfers the frequency to the transmitter over IR.</t>
         </is>
       </c>
     </row>
@@ -6464,1031 +7712,67 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>•  Teradek fixed-frequency locks only exist in the green rows (U-NII-1, U-NII-3, U-NII-5).</t>
+          <t>•  Digital 6000 TX work with EK 6042 in Long-Range (LR) mode — set both to LR.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>•  A 40 MHz link eats two adjacent 20 MHz slots — count both when charting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  Venue Wi-Fi lives in these same bands; 6 GHz (U-NII-5) is usually the cleanest room on site.</t>
+          <t>•  EM 6000 is the rack receiver; EK 6042 is the portable equivalent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Digital 6000 manual</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>https://docs.cloud.sennheiser.com/en-us/digital-6000/digital-6000_instruction_manual_04_2026_en.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>EK 6042 manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2023/https://assets.sennheiser.com/global-downloads/file/12330/EK6042_Manual_06_2019_EN.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="12">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>2.4 GHz Auto-Hop Mics (DJI / Rode / Hollyland)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Consumer digital mics · adaptive frequency hopping · there is no frequency to dial</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>How to reach any MHz</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>CANNOT BE COORDINATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tuning step</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>none — the radio picks its own hops, continuously</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Range / band</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2.400–2.4835 GHz ISM (DJI Mic 3 can also use 5.1–5.8 GHz)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Matching TX &lt;-&gt; RX</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>WHAT THEY ARE  -  All 2.4 GHz ISM, all auto-hop</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>What They Are</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>All 2.4 GHz ISM, all auto-hop</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>DJI Mic / Mic 2 / Mic Mini: 2.400–2.4835 GHz, GFSK, &lt; 20 dBm EIRP (Mic 3 adds 5.1–5.8 GHz).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Rode Wireless GO II / PRO / ME: “Series IV” 2.4 GHz digital, 128-bit encryption, auto-pairing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Hollyland Lark M2 / Max: 2.4 GHz adaptive frequency hopping, &lt; 20 dBm EIRP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>WHAT TO TELL THE CREW  -  Kindly, at the check-in table</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>What To Tell The Crew</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Kindly, at the check-in table</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>These can’t take an assigned frequency — that’s the design, not a setting you’re missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>They share 2.4 GHz with venue Wi-Fi, Bluetooth, ZaxNet, and comms — count them on the walk anyway; every one raises the noise floor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Power off units that aren’t actively shooting; if reliability matters, hand them a coordinated UHF pack instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>RF POWER &amp; SAFE POWER-ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>SATURATION</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Saturation is the endgame: each link needs clean hop-space. Cluster enough of them (plus Wi-Fi, Bluetooth, ZaxNet) in one small area and the band fills — all of them start dropping at once, and no settings menu can fix physics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Fixed by regulation, not by menu: ISM-band devices run &lt; 20 dBm EIRP and must tolerate each other’s interference (FCC Part 15). Range claims (100–400 m LOS) assume a quiet band — an event floor is not one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  Nothing on this card is field-tunable — if a crew insists their unit “has a channel setting,” it’s a pairing menu, not a frequency menu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  DJI Mic 3 in 5 GHz mode lands in the same U-NII bands as Teradek video — see the 5/6 GHz chart card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  These are fine tools in isolation; the problem is density.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>DJI Mic 2 specs</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>https://www.dji.com/mic-2/specs</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Rode Wireless GO II</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>https://rode.com/en-us/microphones/wireless/wirelessgoii</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId2"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sennheiser EW-DX</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Digital UHF · no portable RX in-series — EW-DP EK is the camera option</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>How to reach any MHz</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FREE-TUNE TO ANY MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tuning step</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>fine (MHz + kHz entry; factory presets sit on a 600 kHz grid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Range / band</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>US: Q1-9 470.2–550 · R1-9 520–607.8 · V5-7 941.7–959.65 (licensed STL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Matching TX &lt;-&gt; RX</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Sync runs over Bluetooth LE from the receiver — receiver values overwrite the TX. Manual TX entry and the Smart Assist app also work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TRANSMITTER  -  SK / SKM(-S) (bodypack / handheld)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Transmitter</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>SK / SKM(-S) (bodypack / handheld)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Press [SET] to open the menu -&gt; Frequency; [UP]/[DOWN] sets the MHz range -&gt; [SET] -&gt; [UP]/[DOWN] sets the kHz -&gt; [SET] to save.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Or sync from the receiver: press [CH 1]/CH 2 on the EM 2 -&gt; [SYNC] on the receiver -&gt; short-press [SYNC] on the TX (Bluetooth LE — no IR).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Keep that TX press short — holding [SYNC] &gt; 2 s enters firmware-update mode and cancels the sync.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>PORTABLE RECEIVER  -  EW-DP EK (camera receiver, cross-compatible)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Portable Receiver</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>EW-DP EK (camera receiver, cross-compatible)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>[UP]/[DOWN]/[SET]/[ESC] -&gt; FREQUENCY (or AUTO SCAN / CHANNEL).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Set the assigned MHz; [SET] to save. 3Must be the same frequency-range variant as the TX; EW-DX extras (encryption, LD) drop off on EW-DP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>RF POWER &amp; SAFE POWER-ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>No RF-mute boot combo. SK / SKM-S: set the mute-switch function to RF Mute (TX menu: Mute Button; or RX: Ch -&gt; Mute Mode) and slide to mute before power-on. Plain SKM has no mute switch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Fixed 10 mW ERP (12 mW in Y1-3) — there is no RF-power menu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>•  Enabling AES-256 (System -&gt; Link Encryption) requires re-syncing every TX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  Link Density mode needs a receiver restart; presets shift to a 300 kHz grid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  TX and RX must share the frequency-range variant (Q1-9 vs R1-9…).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  EW-D (non-DX) TXs have no display at all — set the freq on the EW-D EM (or Smart Assist app) and push with the [SYNC] buttons (BLE). Fixed 10 mW. Q1-6 = 470.2–526; “S1-7” = 606.2–662 (mostly not US-legal).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>EW-DX online
-        manual</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>https://docs.cloud.sennheiser.com/en-us/ew-d/ew-d/manual.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Frequency
-        ranges</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>https://docs.cloud.sennheiser.com/en-us/ew-d/ew-d/productinfo-freq-ranges.html</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sennheiser Digital 6000</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Digital UHF · portable (camera) receiver shown</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>How to reach any MHz</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FREE-TUNE TO ANY MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tuning step</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>25 kHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Range / band</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Up to 88–184 MHz tuning, depending on unit</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Matching TX &lt;-&gt; RX</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>On the EM 6000, Sync Settings ▸ Frequency Only pushes just the freq. The EK 6042 sync always transfers the frequency (long-press the sync button for IR).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TRANSMITTER  -  SK 6000 / SKM 6000</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Transmitter</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>SK 6000 / SKM 6000</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>On the TX, press [SET] to open the menu -&gt; Tune.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Set the assigned MHz (25 kHz steps); confirm — saving auto-assigns it to preset U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Match the transmission mode (e.g. LR) to the receiver, or the link won’t form.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>PORTABLE RECEIVER  -  EK 6042 (2-ch camera receiver, LR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Portable Receiver</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>EK 6042 (2-ch camera receiver, LR)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Press the channel button -&gt; CH Settings -&gt; Frequency -&gt; Tune.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Set the same MHz; confirm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Then Sync transfers the frequency to the transmitter over IR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>RF POWER &amp; SAFE POWER-ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>SK 6212: hold [ON/OFF] at power-up until the LED lights red -&gt; boots in RF MUTE. SK 6000 / SKM 6000 have no RF-mute boot — set the freq on the EM 6000 / EK 6042 and IR-sync before the pack goes live. RF POWERSet by mode: LR — SK/SKM 6000 25 mW, SK 6212 15 mW (Low 3.5). LD — 3.5 mW (SKM 6000: 1 mW). Mode is set on the EM 6000 and pushed by sync — not a free dial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>•  Digital 6000 TX work with EK 6042 in Long-Range (LR) mode — set both to LR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  EM 6000 is the rack receiver; EK 6042 is the portable equivalent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7729,84 +8013,424 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>RF Mute: hold [ON/OFF] at switch-on until “RF Mute Off?” shows -&gt; [UP]/[DOWN] to “RF Mute On?” -&gt; [SET]. Tune/sync, then un-mute the same way.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>10 / 30 / 50 mW (US: up to 100 mW) — Advanced ▸ RF Power on the TX.</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  RX and TX must share the same band / range, or they can’t meet on frequency.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  Fixed banks 1–20 are presets only — use a user bank (U1–U6) to land on an arbitrary coordinated MHz.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  RX and TX must share the same band / range, or they can’t meet on frequency.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Fixed banks 1–20 are presets only — use a user bank (U1–U6) to land on an arbitrary coordinated MHz.</t>
+          <t>•  2000 series sits above ew G3/G4 and below 3000/5000 — same 25 kHz raster.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  2000 series sits above ew G3/G4 and below 3000/5000 — same 25 kHz raster.</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SK 2000 manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2021/https://assets.sennheiser.com/global-downloads/file/8549/SK_2000_Manual_12_2016_EN.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>EK 2000 manual</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2025/https://assets.sennheiser.com/global-downloads/file/8545/EK_2000_Manual_12_2016_EN.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="13">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sennheiser 3000 / 5000 Series</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SK 5212-II bodypack · SKM 5200-II handheld · SKP 3000 plug-on — EK 3241 portable receiver</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>How to reach any MHz</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FREE-TUNE TO ANY MHz</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tuning step</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>5 kHz — finest on these cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Range / band</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Tune within the unit’s switching bandwidth (EK 3241 ≈ 36 MHz; SK 5212-II up to 184 MHz); stay in the legal range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Matching TX &lt;-&gt; RX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TRANSMITTER  -  SK 5212(-II) / SKM 5200(-II) / SKP 3000 (bodypack / handheld / plug-on)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>SK 5212(-II) / SKM 5200(-II) / SKP 3000 (bodypack / handheld / plug-on)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Deactivate the autolock if on. Open the menu -&gt; CHAN: pick a VAR-bank channel (FIX-bank presets cannot be changed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Go to TUNE and set the assigned MHz — tunes in 5 kHz steps; press [SET] to store (“STORED”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Set output in POWER, then EXIT. (TUNE / CHAN only take effect once you [SET] them.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PORTABLE RECEIVER  -  EK 3241 (camera receiver)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Notes / Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Portable Receiver</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>EK 3241 (camera receiver)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Use [CHAn] to pick a channel in bank “U” (variable bank, 20 channels U.01–U.20; bank “F” is 32 factory presets).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Open [tunE] and set the same MHz by hand (5 kHz steps); press [SET] (“StorEd”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>No IR sync on this receiver — confirm the MHz matches the TX exactly. (Use an EM 3732 rack if you need IR sync.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RF POWER &amp; SAFE POWER-ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  FIX-bank presets cannot be changed; use the VAR bank to land on a coordinated MHz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  EK 3241 has no transmitter IR-sync — match by hand (or sync from an EM 3732 rack).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>•  TX and RX must share the same range / band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SK 5212-II manual</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2024/https://assets.sennheiser.com/global-downloads/file/6846/SK_5212-II_Manual_11_2010_EN.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>EK 3241 manual (US)</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2021/https://assets.sennheiser.com/global-downloads/file/12024/EK_3241_532026_0209_INT_US.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>EM 3732-II manual</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2021/https://assets.sennheiser.com/global-downloads/file/10500/EM_3732-II_Manual_10_2019_EN.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7825,14 +8449,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sennheiser 3000 / 5000 Series</t>
+          <t>Shure SLX-D</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SK 5212-II bodypack · SKM 5200-II handheld · SKP 3000 plug-on — EK 3241 portable receiver</t>
+          <t>Digital UHF · SLXD5 is the portable receiver</t>
         </is>
       </c>
     </row>
@@ -7863,7 +8487,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>5 kHz — finest on these cards</t>
+          <t>25 kHz (JB band 125 kHz)</t>
         </is>
       </c>
     </row>
@@ -7875,7 +8499,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Tune within the unit’s switching bandwidth (EK 3241 ≈ 36 MHz; SK 5212-II up to 184 MHz); stay in the legal range.</t>
+          <t>US: G58 470–514 · H55 514–558 · J52 558–602 + 614–616 · wideband “+” models G57 470–608</t>
         </is>
       </c>
     </row>
@@ -7885,16 +8509,12 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>The EK 3241 camera receiver has no IR transmitter-sync — match the frequency by hand on both ends (5 kHz). An EM 3732 rack can IR-sync the transmitters if you have one.</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TRANSMITTER  -  SK 5212(-II) / SKM 5200(-II) / SKP 3000 (bodypack / handheld / plug-on)</t>
+          <t>TRANSMITTER  -  SLXD1 / SLXD2 (bodypack / handheld)</t>
         </is>
       </c>
     </row>
@@ -7933,7 +8553,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>SK 5212(-II) / SKM 5200(-II) / SKP 3000 (bodypack / handheld / plug-on)</t>
+          <t>SLXD1 / SLXD2 (bodypack / handheld)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -7941,7 +8561,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Deactivate the autolock if on. Open the menu -&gt; CHAN: pick a VAR-bank channel (FIX-bank presets cannot be changed).</t>
+          <t>Transmitters have no frequency menu (menu = RF power, offset, locks) — the frequency comes from the receiver.</t>
         </is>
       </c>
     </row>
@@ -7951,7 +8571,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Go to TUNE and set the assigned MHz — tunes in 5 kHz steps; press [SET] to store (“STORED”).</t>
+          <t>Tune the receiver (right), align the IR ports, press the receiver’s [sync] button -&gt; the TX takes the freq.</t>
         </is>
       </c>
     </row>
@@ -7961,14 +8581,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Set output in POWER, then EXIT. (TUNE / CHAN only take effect once you [SET] them.)</t>
+          <t>No RF-mute boot exists on SLX-D — power packs up away from the rig, sync, then move in.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PORTABLE RECEIVER  -  EK 3241 (camera receiver)</t>
+          <t>PORTABLE RECEIVER  -  SLXD5 (portable slot/bag receiver)</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8627,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>EK 3241 (camera receiver)</t>
+          <t>SLXD5 (portable slot/bag receiver)</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -8015,7 +8635,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Use [CHAn] to pick a channel in bank “U” (variable bank, 20 channels U.01–U.20; bank “F” is 32 factory presets).</t>
+          <t>Press [Enter] from home -&gt; Frequency -&gt; Manual Setup (or Channel / Group Scan).</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8645,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Open [tunE] and set the same MHz by hand (5 kHz steps); press [SET] (“StorEd”).</t>
+          <t>[▲▼] arrows to set G / C or the exact MHz (25 kHz); [Enter] to apply.</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8655,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>No IR sync on this receiver — confirm the MHz matches the TX exactly. (Use an EM 3732 rack if you need IR sync.)</t>
+          <t>Align IR ports with the TX and press [Sync].</t>
         </is>
       </c>
     </row>
@@ -8046,90 +8666,96 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>No standby-off boot — set the freq in TUNE (and a low POWER level) before the pack is near other rigs; confirm, then raise power / go live.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>SK 5212-II POWER menu: 50 mW (PWR.HI) / 10 mW (PWR.LO) / 10 mW low-intermod (LoI).</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  Legacy SLX-D has no encryption; SLX-D+ adds AES-256.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>•  G65 and L57 are not US bands — US stock is G58 / H55 / J52 (+ G57 wideband).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>•  FIX-bank presets cannot be changed; use the VAR bank to land on a coordinated MHz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  EK 3241 has no transmitter IR-sync — match by hand (or sync from an EM 3732 rack).</t>
+          <t>•  Keep all receivers in one band on the same group.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>•  TX and RX must share the same range / band.</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SLX-D user guide</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://pubs.shure.com/guide/SLXD</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SLXD4Q+ user guide</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://pubs.shure.com/guide/SLXD4Qplus</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="13">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8142,14 +8768,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Shure SLX-D</t>
+          <t>Shure ULX-D</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Digital UHF · SLXD5 is the portable receiver</t>
+          <t>Digital UHF · (no portable receiver — half-rack ULXD4 shown)</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8806,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>25 kHz (JB band 125 kHz)</t>
+          <t>25 kHz</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8818,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>US: G58 470–514 · H55 514–558 · J52 558–602 + 614–616 · wideband “+” models G57 470–608</t>
+          <t>Band on the label must match (e.g. G50 = 470–534 MHz)</t>
         </is>
       </c>
     </row>
@@ -8202,16 +8828,12 @@
           <t>Matching TX &lt;-&gt; RX</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>SLXD4 path: push the control knob -&gt; Frequency Setup ▸ Manual Frequency Setup -&gt; set G / C / MHz -&gt; Apply. “+” receivers pair with legacy TXs when RF Band matches (Device Configuration ▸ RF ▸ RF Band).</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TRANSMITTER  -  SLXD1 / SLXD2 (bodypack / handheld)</t>
+          <t>TRANSMITTER  -  ULXD1 / ULXD2 (bodypack / handheld)</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8872,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>SLXD1 / SLXD2 (bodypack / handheld)</t>
+          <t>ULXD1 / ULXD2 (bodypack / handheld)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -8258,7 +8880,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Transmitters have no frequency menu (menu = RF power, offset, locks) — the frequency comes from the receiver.</t>
+          <t>ULXD1/2 have no frequency menu — the TX menu covers mute mode, mic offset and locks only. The frequency comes from the receiver.</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8890,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Tune the receiver (right), align the IR ports, press the receiver’s [sync] button -&gt; the TX takes the freq.</t>
+          <t>Tune the receiver channel (right), align IR windows, press [SYNC] -&gt; the TX takes the frequency.</t>
         </is>
       </c>
     </row>
@@ -8278,14 +8900,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>No RF-mute boot exists on SLX-D — power packs up away from the rig, sync, then move in.</t>
+          <t>Need RF silence meanwhile? Hold [exit] while powering the TX on until RF MUTED shows.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PORTABLE RECEIVER  -  SLXD5 (portable slot/bag receiver)</t>
+          <t>PORTABLE RECEIVER  -  ULXD4 (half-rack receiver)</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8946,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>SLXD5 (portable slot/bag receiver)</t>
+          <t>ULXD4 (half-rack receiver)</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -8332,7 +8954,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Press [Enter] from home -&gt; Frequency -&gt; Manual Setup (or Channel / Group Scan).</t>
+          <t>Open the channel’s RADIO screen; push the [control wheel] to edit.</t>
         </is>
       </c>
     </row>
@@ -8342,134 +8964,94 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>[▲▼] arrows to set G / C or the exact MHz (25 kHz); [Enter] to apply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+          <t>Rotate to the Frequency field and set the assigned MHz directly; [ENTER] to save.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Align IR windows, press [SYNC] -&gt; Sync Success copies it to the TX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>RF POWER &amp; SAFE POWER-ON</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Nothing to hold at boot — this family has no RF-mute power-on (unlike ULX-D). Set the receiver first, sync at a distance, then approach.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>TX menu RF Power: 1 / 10 mW (SLXD3 plug-on: 30 mW); or push from the SLXD5 (TX ▸ RF Power, Low 1 / High 10) via IR sync.</t>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  ULX-D has no bodypack/portable receiver — all receivers are rack/half-rack.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>•  Legacy SLX-D has no encryption; SLX-D+ adds AES-256.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  G65 and L57 are not US bands — US stock is G58 / H55 / J52 (+ G57 wideband).</t>
+          <t>•  Re-sync after enabling/disabling encryption. Mixed bands are OK if both units can tune the same frequency (Shure “Mixed-Band Operation”).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Keep all receivers in one band on the same group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>SLX-D user
-        guide</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>https://pubs.shure.com/guide/SLXD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>SLXD4Q+ user guide</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>https://pubs.shure.com/guide/SLXD4Qplus</t>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ULX-D user guide</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>https://pubs.shure.com/view/guide/ULXD/en-US.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B23:E23"/>
+  <mergeCells count="10">
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C29:E29"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8482,14 +9064,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Shure ULX-D</t>
+          <t>Shure Axient Digital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Digital UHF · (no portable receiver — half-rack ULXD4 shown)</t>
+          <t>Digital UHF · portable receiver shown</t>
         </is>
       </c>
     </row>
@@ -8532,7 +9114,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Band on the label must match (e.g. G50 = 470–534 MHz)</t>
+          <t>US: G57 470–616 (608–614 gap) · K54 606–663 · X55 941–960 — intl: G55/G56 470–636 · K57 606–790 MHz</t>
         </is>
       </c>
     </row>
@@ -8544,14 +9126,14 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>In the RADIO menu you can set Group/Channel or edit the Frequency field for an exact coordinated MHz.</t>
+          <t>Channels are grouped for intermod safety, but you can type an exact Frequency on either device.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TRANSMITTER  -  ULXD1 / ULXD2 (bodypack / handheld)</t>
+          <t>TRANSMITTER  -  AD1/ADX1 · AD2/ADX2 (pack/handheld)</t>
         </is>
       </c>
     </row>
@@ -8590,7 +9172,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>ULXD1 / ULXD2 (bodypack / handheld)</t>
+          <t>AD1/ADX1 · AD2/ADX2 (pack/handheld)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -8598,7 +9180,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ULXD1/2 have no frequency menu — the TX menu covers mute mode, mic offset and locks only. The frequency comes from the receiver.</t>
+          <t>On the TX, [O] -&gt; Radio -&gt; Freq; [O] once edits the first 3 digits, twice the last 3; [∧∨] to set the assigned MHz; [O] to save.</t>
         </is>
       </c>
     </row>
@@ -8608,315 +9190,6 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Tune the receiver channel (right), align IR windows, press [SYNC] -&gt; the TX takes the frequency.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Need RF silence meanwhile? Hold [exit] while powering the TX on until RF MUTED shows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>PORTABLE RECEIVER  -  ULXD4 (half-rack receiver)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Portable Receiver</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>ULXD4 (half-rack receiver)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Open the channel’s RADIO screen; push the control wheel to edit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Rotate to the Frequency field and set the assigned MHz directly; [ENTER] to save.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Align IR windows, press [SYNC] -&gt; Sync Success copies it to the TX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>RF POWER &amp; SAFE POWER-ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Hold [exit] during TX power-on until RF MUTED displays. Sync the assigned freq from the receiver, then restart the TX to un-mute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>1 / 10 / 20 mW — pushed from the receiver as an IR-sync preset (Lo 1 / Nm 10 / Hi 20), not set on the TX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  ULX-D has no bodypack/portable receiver — all receivers are rack/half-rack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  Re-sync after enabling/disabling encryption. Mixed bands are OK if both units can tune the same frequency (Shure “Mixed-Band Operation”).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shure Axient Digital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Digital UHF · portable receiver shown</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>How to reach any MHz</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FREE-TUNE TO ANY MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tuning step</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>25 kHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Range / band</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>US: G57 470–616 (608–614 gap) · K54 606–663 · X55 941–960 — intl: G55/G56 470–636 · K57 606–790 MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Matching TX &lt;-&gt; RX</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Channels are grouped for intermod safety, but you can type an exact Frequency on either device.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TRANSMITTER  -  AD1/ADX1 · AD2/ADX2 (pack/handheld)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Notes / Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Transmitter</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>AD1/ADX1 · AD2/ADX2 (pack/handheld)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>On the TX, [O] -&gt; Radio -&gt; Freq; [O] once edits the first 3 digits, twice the last 3; [∧∨] to set the assigned MHz; [O] to save.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
           <t>Or IR-sync from the receiver (right). ADX can also be re-tuned remotely via ShowLink / AD610.</t>
         </is>
       </c>
@@ -9002,128 +9275,99 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>RF OFF FIRST</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Hold [X] while powering on -&gt; SAFE START menu -&gt; set RF: Mute (persists through power cycles). Tune/sync, then un-mute: Radio -&gt; Output -&gt; On.</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RF POWER</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>AD 2 / 10 / 35 mW · ADX 2 / 10 / 40 mW (Radio -&gt; Power; some bands 2 / 10 only; 10 mW max above 608 MHz).</t>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>WATCH OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>•  Receiver RF Band must equal the TX band; after changing RF band, re-sync every TX.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>WATCH OUT</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>•  ADX5D is the portable receiver; AD4D/AD4Q are the rack versions.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>•  Receiver RF Band must equal the TX band; after changing RF band, re-sync every TX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>•  ADX5D is the portable receiver; AD4D/AD4Q are the rack versions.</t>
+          <t>•  G57+ (ADX5D) extends G57 with 614–616 MHz; TX power is capped at 10 mW there.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>•  G57+ (ADX5D) extends G57 with 614–616 MHz; TX power is capped at 10 mW there.</t>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ADX1 guide (Safe Start, tuning)</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>https://pubs.shure.com/view/guide/ADX1/en-US.pdf</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ADX5D guide (sync, bands)</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>https://pubs.shure.com/view/guide/ADX5D/en-US.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>ADX1
-        guide (Safe Start, tuning)</t>
+          <t>AD frequency chart</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>https://pubs.shure.com/view/guide/ADX1/en-US.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>ADX5D guide (sync,
-        bands)</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>https://pubs.shure.com/view/guide/ADX5D/en-US.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>AD
-        frequency chart</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
           <t>https://content-files.shure.com/Pubs/AxientDigital/Axient_Digital_Frequency_Chart.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="C33:E33"/>
+  <mergeCells count="15">
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quick-dial-cards-editable.xlsx
+++ b/quick-dial-cards-editable.xlsx
@@ -1794,7 +1794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2083,17 +2083,29 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>UWP-D operating instructions</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://pro.sony/support/res/manuals/5009/96c5bb8845154ae1e06fbe70a175ad9d/50099341M.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>UWP frequency lists</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>https://pro.sony/support/res/manuals/4530/63d2501a47358304ae6fe7185a0a2c9c/45307382M.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A16:E16"/>
@@ -2101,14 +2113,17 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C32:E32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
